--- a/InterFace_FINAL_QLHS/Template/Mau_Import_HS.xlsx
+++ b/InterFace_FINAL_QLHS/Template/Mau_Import_HS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23BITV01\C#\InterFace_FINAL_QLHS\InterFace_FINAL_QLHS\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC9B93F-186F-490D-988B-D244333DC351}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5DCA09-10B5-4601-88A7-AA7A2B543552}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0820006-BCF0-4F5B-8215-38C9EC591A0F}"/>
   </bookViews>
@@ -29,9 +29,62 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Họ Và Tên HS</t>
+  </si>
+  <si>
+    <t>Ngày Tháng năm sinh</t>
+  </si>
+  <si>
+    <t>Giới Tính</t>
+  </si>
+  <si>
+    <t>Địa chỉ</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Khối lớp</t>
+  </si>
+  <si>
+    <t>Họ tên Phụ Huynh</t>
+  </si>
+  <si>
+    <t>Ngày Tiếp Nhận</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>TP HCM</t>
+  </si>
+  <si>
+    <t>AN@gmail.com</t>
+  </si>
+  <si>
+    <t>0986876567</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị B</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,6 +98,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -54,7 +122,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,15 +130,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -383,13 +486,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD15721B-2997-489F-B281-082654BA29B3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="14.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="14.28515625" style="1"/>
+    <col min="1" max="1" width="28.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="14.28515625" style="1"/>
+    <col min="5" max="5" width="19.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1"/>
+    <col min="8" max="8" width="25.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.5703125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="14.28515625" style="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7">
+        <v>38681</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="6">
+        <v>10</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="7">
+        <v>45767</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{2AD504B3-F2E1-42EC-A9CA-29FEB653DF87}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>